--- a/utils/data-room-simulator/output/balance_sheet.xlsx
+++ b/utils/data-room-simulator/output/balance_sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,107 +417,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>period_end</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>accounts_receivable</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>prepaid_expenses</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_current_assets</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fixed_assets</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>accumulated_depreciation</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>net_fixed_assets</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_assets</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>accounts_payable</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>accrued_expenses</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>deferred_revenue</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>line_of_credit</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>total_current_liabilities</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>total_liabilities</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>common_stock</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>retained_earnings</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>total_equity</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>balance_check</t>
         </is>
@@ -545,54 +533,54 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6036389.43</v>
+        <v>2278794.93</v>
       </c>
       <c r="D2" t="n">
-        <v>6102853.62</v>
+        <v>3944970.63</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>83915.96000000001</v>
+        <v>53447.76</v>
       </c>
       <c r="G2" t="n">
-        <v>12223159.01</v>
+        <v>6277213.32</v>
       </c>
       <c r="H2" t="n">
-        <v>6303672.84</v>
+        <v>3467576.21</v>
       </c>
       <c r="I2" t="n">
-        <v>372020.04</v>
+        <v>201343.13</v>
       </c>
       <c r="J2" t="n">
-        <v>5931652.8</v>
+        <v>3266233.08</v>
       </c>
       <c r="K2" t="n">
-        <v>18154811.81</v>
+        <v>9543446.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1760429.06</v>
+        <v>991313.83</v>
       </c>
       <c r="M2" t="n">
-        <v>125873.95</v>
+        <v>80171.64</v>
       </c>
       <c r="N2" t="n">
-        <v>5832440.58</v>
+        <v>3893107.89</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>7718743.58</v>
+        <v>4964593.35</v>
       </c>
       <c r="R2" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S2" t="n">
-        <v>8380075.78</v>
+        <v>3447875.81</v>
       </c>
       <c r="T2" t="n">
-        <v>10436068.23</v>
+        <v>4578853.05</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -608,54 +596,54 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14458186.02</v>
+        <v>6353177.99</v>
       </c>
       <c r="D3" t="n">
-        <v>6483673.45</v>
+        <v>5329744.37</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>86966.82000000001</v>
+        <v>70062.03999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>21028826.29</v>
+        <v>11752984.4</v>
       </c>
       <c r="H3" t="n">
-        <v>6451704.29</v>
+        <v>3549006.57</v>
       </c>
       <c r="I3" t="n">
-        <v>761512.64</v>
+        <v>412142.7</v>
       </c>
       <c r="J3" t="n">
-        <v>5690191.65</v>
+        <v>3136863.87</v>
       </c>
       <c r="K3" t="n">
-        <v>26719017.93</v>
+        <v>14889848.27</v>
       </c>
       <c r="L3" t="n">
-        <v>1919474.2</v>
+        <v>1462286.08</v>
       </c>
       <c r="M3" t="n">
-        <v>130450.23</v>
+        <v>105093.06</v>
       </c>
       <c r="N3" t="n">
-        <v>5457523.4</v>
+        <v>4280651.56</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>7507447.83</v>
+        <v>5848030.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S3" t="n">
-        <v>17155577.66</v>
+        <v>7910840.34</v>
       </c>
       <c r="T3" t="n">
-        <v>19211570.1</v>
+        <v>9041817.58</v>
       </c>
       <c r="U3" t="b">
         <v>1</v>
@@ -671,54 +659,54 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23547032.47</v>
+        <v>12140794.24</v>
       </c>
       <c r="D4" t="n">
-        <v>6911431.68</v>
+        <v>6328290.97</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>94521.74000000001</v>
+        <v>80836.32000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>30552985.89</v>
+        <v>18549921.53</v>
       </c>
       <c r="H4" t="n">
-        <v>6599735.75</v>
+        <v>3630436.93</v>
       </c>
       <c r="I4" t="n">
-        <v>1168477.8</v>
+        <v>632398.6899999999</v>
       </c>
       <c r="J4" t="n">
-        <v>5431257.95</v>
+        <v>2998038.24</v>
       </c>
       <c r="K4" t="n">
-        <v>35984243.83</v>
+        <v>21547959.77</v>
       </c>
       <c r="L4" t="n">
-        <v>1845152.43</v>
+        <v>1686794.4</v>
       </c>
       <c r="M4" t="n">
-        <v>141782.61</v>
+        <v>121254.47</v>
       </c>
       <c r="N4" t="n">
-        <v>5535191.95</v>
+        <v>5352768.61</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>7522126.99</v>
+        <v>7160817.48</v>
       </c>
       <c r="R4" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S4" t="n">
-        <v>26406124.4</v>
+        <v>13256165.05</v>
       </c>
       <c r="T4" t="n">
-        <v>28462116.84</v>
+        <v>14387142.28</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -734,54 +722,54 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31034709.67</v>
+        <v>18968114.18</v>
       </c>
       <c r="D5" t="n">
-        <v>9136272.58</v>
+        <v>7000183.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>110626.03</v>
+        <v>94970.28</v>
       </c>
       <c r="G5" t="n">
-        <v>40281608.28</v>
+        <v>26063267.79</v>
       </c>
       <c r="H5" t="n">
-        <v>6747767.2</v>
+        <v>3711867.29</v>
       </c>
       <c r="I5" t="n">
-        <v>1592915.54</v>
+        <v>862111.11</v>
       </c>
       <c r="J5" t="n">
-        <v>5154851.66</v>
+        <v>2849756.18</v>
       </c>
       <c r="K5" t="n">
-        <v>45436459.96</v>
+        <v>28913023.97</v>
       </c>
       <c r="L5" t="n">
-        <v>1792108.45</v>
+        <v>2427345.02</v>
       </c>
       <c r="M5" t="n">
-        <v>165939.05</v>
+        <v>142455.42</v>
       </c>
       <c r="N5" t="n">
-        <v>5432796.96</v>
+        <v>5829430.93</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>7390844.46</v>
+        <v>8399231.369999999</v>
       </c>
       <c r="R5" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S5" t="n">
-        <v>35989623.05</v>
+        <v>19382815.36</v>
       </c>
       <c r="T5" t="n">
-        <v>38045615.5</v>
+        <v>20513792.6</v>
       </c>
       <c r="U5" t="b">
         <v>1</v>
@@ -797,54 +785,54 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44801221.68</v>
+        <v>24988416.19</v>
       </c>
       <c r="D6" t="n">
-        <v>9757656.48</v>
+        <v>8829223.939999999</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>126035.34</v>
+        <v>112180.71</v>
       </c>
       <c r="G6" t="n">
-        <v>54684913.5</v>
+        <v>33929820.84</v>
       </c>
       <c r="H6" t="n">
-        <v>6895798.66</v>
+        <v>3793297.66</v>
       </c>
       <c r="I6" t="n">
-        <v>2034825.83</v>
+        <v>1101279.96</v>
       </c>
       <c r="J6" t="n">
-        <v>4860972.83</v>
+        <v>2692017.7</v>
       </c>
       <c r="K6" t="n">
-        <v>59545886.33</v>
+        <v>36621838.52</v>
       </c>
       <c r="L6" t="n">
-        <v>2734211.06</v>
+        <v>2223664.41</v>
       </c>
       <c r="M6" t="n">
-        <v>189053.02</v>
+        <v>168271.06</v>
       </c>
       <c r="N6" t="n">
-        <v>6938550.12</v>
+        <v>6259935.44</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>9861814.199999999</v>
+        <v>8651870.91</v>
       </c>
       <c r="R6" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S6" t="n">
-        <v>47628079.69</v>
+        <v>26838990.38</v>
       </c>
       <c r="T6" t="n">
-        <v>49684072.13</v>
+        <v>27969967.61</v>
       </c>
       <c r="U6" t="b">
         <v>1</v>
@@ -856,58 +844,58 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45962230.7</v>
+        <v>27576137.3</v>
       </c>
       <c r="D7" t="n">
-        <v>7319927.28</v>
+        <v>5693644.51</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>93866.64</v>
+        <v>85291.71000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>53376024.62</v>
+        <v>33355073.52</v>
       </c>
       <c r="H7" t="n">
-        <v>6908134.61</v>
+        <v>3806869.38</v>
       </c>
       <c r="I7" t="n">
-        <v>2072440.38</v>
+        <v>1142060.81</v>
       </c>
       <c r="J7" t="n">
-        <v>4835694.23</v>
+        <v>2664808.57</v>
       </c>
       <c r="K7" t="n">
-        <v>58211718.86</v>
+        <v>36019882.08</v>
       </c>
       <c r="L7" t="n">
-        <v>2044253.93</v>
+        <v>1986978.94</v>
       </c>
       <c r="M7" t="n">
-        <v>140799.96</v>
+        <v>127937.56</v>
       </c>
       <c r="N7" t="n">
-        <v>5441473.07</v>
+        <v>4758451.49</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>7626526.96</v>
+        <v>6873367.99</v>
       </c>
       <c r="R7" t="n">
-        <v>2055992.44</v>
+        <v>1130977.24</v>
       </c>
       <c r="S7" t="n">
-        <v>48529199.45</v>
+        <v>28015536.86</v>
       </c>
       <c r="T7" t="n">
-        <v>50585191.9</v>
+        <v>29146514.09</v>
       </c>
       <c r="U7" t="b">
         <v>1</v>
